--- a/ru/downloads/data-excel/3.2.2.xlsx
+++ b/ru/downloads/data-excel/3.2.2.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F49E74-EF36-4B39-9E86-DFA501C1AFD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23130" windowHeight="9450"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -154,7 +155,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -311,18 +312,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -334,29 +332,20 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -364,62 +353,40 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
-    <cellStyle name="Обычный 4" xfId="2"/>
-    <cellStyle name="Обычный 6" xfId="3"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Обычный 4" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный 6" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -435,9 +402,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -475,9 +442,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -512,7 +479,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -547,7 +514,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -720,11 +687,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T34"/>
+  <dimension ref="A1:U34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.85546875" customWidth="1"/>
@@ -732,37 +699,26 @@
     <col min="4" max="17" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="16" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:21" s="12" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
       <c r="Q1"/>
     </row>
-    <row r="2" spans="1:20" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+    <row r="2" spans="1:21" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="11" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="1"/>
@@ -773,14 +729,14 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
-      <c r="L2" s="2"/>
+      <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="5"/>
+    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -789,1930 +745,2023 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-      <c r="L3" s="2"/>
+      <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
     </row>
-    <row r="4" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="18">
         <v>2007</v>
       </c>
-      <c r="E4" s="23">
+      <c r="E4" s="18">
         <v>2008</v>
       </c>
-      <c r="F4" s="23">
+      <c r="F4" s="18">
         <v>2009</v>
       </c>
-      <c r="G4" s="23">
+      <c r="G4" s="18">
         <v>2010</v>
       </c>
-      <c r="H4" s="23">
+      <c r="H4" s="18">
         <v>2011</v>
       </c>
-      <c r="I4" s="24">
+      <c r="I4" s="18">
         <v>2012</v>
       </c>
-      <c r="J4" s="24">
+      <c r="J4" s="18">
         <v>2013</v>
       </c>
-      <c r="K4" s="24">
+      <c r="K4" s="18">
         <v>2014</v>
       </c>
-      <c r="L4" s="23">
+      <c r="L4" s="18">
         <v>2015</v>
       </c>
-      <c r="M4" s="24">
+      <c r="M4" s="18">
         <v>2016</v>
       </c>
-      <c r="N4" s="24">
+      <c r="N4" s="18">
         <v>2017</v>
       </c>
-      <c r="O4" s="24">
+      <c r="O4" s="18">
         <v>2018</v>
       </c>
-      <c r="P4" s="24">
+      <c r="P4" s="18">
         <v>2019</v>
       </c>
-      <c r="Q4" s="24">
+      <c r="Q4" s="18">
         <v>2020</v>
       </c>
-      <c r="R4" s="24">
+      <c r="R4" s="18">
         <v>2021</v>
       </c>
-      <c r="S4" s="24">
+      <c r="S4" s="18">
         <v>2022</v>
       </c>
-      <c r="T4" s="24">
+      <c r="T4" s="18">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="U4" s="18">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="19">
         <v>21.06270943034945</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="19">
         <v>19.63371344202557</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="19">
         <v>18.141024694820437</v>
       </c>
-      <c r="G5" s="25">
+      <c r="G5" s="19">
         <v>16.397144871101741</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="19">
         <v>15.346362591235996</v>
       </c>
-      <c r="I5" s="25">
+      <c r="I5" s="19">
         <v>14.627093042771016</v>
       </c>
-      <c r="J5" s="25">
+      <c r="J5" s="19">
         <v>14.891975308641975</v>
       </c>
-      <c r="K5" s="25">
+      <c r="K5" s="19">
         <v>15.641512115837417</v>
       </c>
-      <c r="L5" s="25">
+      <c r="L5" s="19">
         <v>13.997993294667548</v>
       </c>
-      <c r="M5" s="25">
+      <c r="M5" s="19">
         <v>12.67071320182094</v>
       </c>
-      <c r="N5" s="25">
+      <c r="N5" s="19">
         <v>11.795339148548367</v>
       </c>
-      <c r="O5" s="25">
+      <c r="O5" s="19">
         <v>11.989552962623211</v>
       </c>
-      <c r="P5" s="25">
+      <c r="P5" s="19">
         <v>11.793594798367574</v>
       </c>
-      <c r="Q5" s="25">
+      <c r="Q5" s="19">
         <v>11.7</v>
       </c>
-      <c r="R5" s="25">
+      <c r="R5" s="19">
         <v>11.9</v>
       </c>
-      <c r="S5" s="25">
+      <c r="S5" s="19">
         <v>10.071559327675153</v>
       </c>
-      <c r="T5" s="25">
+      <c r="T5" s="19">
         <v>10.734567774375416</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="U5" s="19">
+        <v>9.8775806692826471</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="20">
         <v>22.790763743114631</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="20">
         <v>22.288148486231552</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="20">
         <v>19.921802271457832</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="20">
         <v>18.289259071098158</v>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="20">
         <v>16.768074212082915</v>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="20">
         <v>16.123559498824978</v>
       </c>
-      <c r="J6" s="26">
+      <c r="J6" s="20">
         <v>16.540713677994095</v>
       </c>
-      <c r="K6" s="26">
+      <c r="K6" s="20">
         <v>16.894648428125748</v>
       </c>
-      <c r="L6" s="26">
+      <c r="L6" s="20">
         <v>15.428233904311874</v>
       </c>
-      <c r="M6" s="26">
+      <c r="M6" s="20">
         <v>13.418192114042323</v>
       </c>
-      <c r="N6" s="26">
+      <c r="N6" s="20">
         <v>13.094077272784833</v>
       </c>
-      <c r="O6" s="26">
+      <c r="O6" s="20">
         <v>13.215508319401323</v>
       </c>
-      <c r="P6" s="26">
+      <c r="P6" s="20">
         <v>12.876696896299217</v>
       </c>
-      <c r="Q6" s="26">
+      <c r="Q6" s="20">
         <v>12.5</v>
       </c>
-      <c r="R6" s="26">
+      <c r="R6" s="20">
         <v>13.1</v>
       </c>
-      <c r="S6" s="26">
+      <c r="S6" s="20">
         <v>10.551906067345987</v>
       </c>
-      <c r="T6" s="26">
+      <c r="T6" s="20">
         <v>11.465104173618249</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="U6" s="20">
+        <v>10.890190578335121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="20">
         <v>19.234622320176317</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="20">
         <v>16.801402551865198</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="20">
         <v>16.247658783938117</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="20">
         <v>14.412898703119524</v>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="20">
         <v>13.848666602616012</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="20">
         <v>13.046652067157742</v>
       </c>
-      <c r="J7" s="26">
+      <c r="J7" s="20">
         <v>13.148843854172178</v>
       </c>
-      <c r="K7" s="26">
+      <c r="K7" s="20">
         <v>14.310654620060403</v>
       </c>
-      <c r="L7" s="26">
+      <c r="L7" s="20">
         <v>12.46161264942514</v>
       </c>
-      <c r="M7" s="26">
+      <c r="M7" s="20">
         <v>11.881394048903505</v>
       </c>
-      <c r="N7" s="26">
+      <c r="N7" s="20">
         <v>10.421550373059354</v>
       </c>
-      <c r="O7" s="26">
+      <c r="O7" s="20">
         <v>10.694287568191104</v>
       </c>
-      <c r="P7" s="26">
+      <c r="P7" s="20">
         <v>10.6587660383149</v>
       </c>
-      <c r="Q7" s="26">
+      <c r="Q7" s="20">
         <v>11</v>
       </c>
-      <c r="R7" s="26">
+      <c r="R7" s="20">
         <v>10.6</v>
       </c>
-      <c r="S7" s="26">
+      <c r="S7" s="20">
         <v>9.5619606820956751</v>
       </c>
-      <c r="T7" s="26">
+      <c r="T7" s="20">
         <v>9.9642525403214446</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="U7" s="20">
+        <v>8.7896828327892109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="19">
         <v>20.020581906632987</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="19">
         <v>20.371251784864352</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="19">
         <v>17.75295882647108</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="19">
         <v>17.905102954341988</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="19">
         <v>15.91196371477433</v>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="19">
         <v>13.333333333333334</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="19">
         <v>13.292290471526513</v>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="19">
         <v>12.498301861160169</v>
       </c>
-      <c r="L8" s="25">
+      <c r="L8" s="19">
         <v>11.21983039791259</v>
       </c>
-      <c r="M8" s="25">
+      <c r="M8" s="19">
         <v>10.610820244328098</v>
       </c>
-      <c r="N8" s="25">
+      <c r="N8" s="19">
         <v>10.611457405758385</v>
       </c>
-      <c r="O8" s="25">
+      <c r="O8" s="19">
         <v>9.3401424539712394</v>
       </c>
-      <c r="P8" s="25">
+      <c r="P8" s="19">
         <v>10.465116279069766</v>
       </c>
-      <c r="Q8" s="25">
+      <c r="Q8" s="19">
         <v>11.1</v>
       </c>
-      <c r="R8" s="25">
+      <c r="R8" s="19">
         <v>11</v>
       </c>
-      <c r="S8" s="25">
+      <c r="S8" s="19">
         <v>8.2747510251903922</v>
       </c>
-      <c r="T8" s="25">
+      <c r="T8" s="19">
         <v>8.0365048014710894</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="U8" s="19">
+        <v>6.3893227317904309</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="20">
         <v>22.68262189676728</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="20">
         <v>23.757707653246282</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="20">
         <v>19.408054342552159</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="20">
         <v>19.501466275659823</v>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="20">
         <v>16.975974679902173</v>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="20">
         <v>15.115129255544568</v>
       </c>
-      <c r="J9" s="26">
+      <c r="J9" s="20">
         <v>15.365952284674485</v>
       </c>
-      <c r="K9" s="26">
+      <c r="K9" s="20">
         <v>14.723281188379124</v>
       </c>
-      <c r="L9" s="26">
+      <c r="L9" s="20">
         <v>12.076990816454899</v>
       </c>
-      <c r="M9" s="26">
+      <c r="M9" s="20">
         <v>10.41095890410959</v>
       </c>
-      <c r="N9" s="26">
+      <c r="N9" s="20">
         <v>11.745939675174014</v>
       </c>
-      <c r="O9" s="26">
+      <c r="O9" s="20">
         <v>10.395010395010395</v>
       </c>
-      <c r="P9" s="26">
+      <c r="P9" s="20">
         <v>10.332950631458095</v>
       </c>
-      <c r="Q9" s="26">
+      <c r="Q9" s="20">
         <v>11.9</v>
       </c>
-      <c r="R9" s="26">
+      <c r="R9" s="20">
         <v>10</v>
       </c>
-      <c r="S9" s="26">
+      <c r="S9" s="20">
         <v>7.6325088339222615</v>
       </c>
-      <c r="T9" s="26">
+      <c r="T9" s="20">
         <v>7.3384877473463499</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+      <c r="U9" s="20">
+        <v>7.2362927915391033</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="20">
         <v>17.092337917485263</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="20">
         <v>16.629933880985774</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="20">
         <v>15.99312123817713</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="20">
         <v>16.251518833535844</v>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="20">
         <v>14.773776546629731</v>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="20">
         <v>11.456628477905074</v>
       </c>
-      <c r="J10" s="26">
+      <c r="J10" s="20">
         <v>11.054545454545455</v>
       </c>
-      <c r="K10" s="26">
+      <c r="K10" s="20">
         <v>10.119465917076598</v>
       </c>
-      <c r="L10" s="26">
+      <c r="L10" s="20">
         <v>10.296707763175721</v>
       </c>
-      <c r="M10" s="26">
+      <c r="M10" s="20">
         <v>10.818505338078293</v>
       </c>
-      <c r="N10" s="26">
+      <c r="N10" s="20">
         <v>9.4224924012158056</v>
       </c>
-      <c r="O10" s="26">
+      <c r="O10" s="20">
         <v>8.2104091288616754</v>
       </c>
-      <c r="P10" s="26">
+      <c r="P10" s="20">
         <v>10.600706713780919</v>
       </c>
-      <c r="Q10" s="26">
+      <c r="Q10" s="20">
         <v>10.199999999999999</v>
       </c>
-      <c r="R10" s="26">
+      <c r="R10" s="20">
         <v>12</v>
       </c>
-      <c r="S10" s="26">
+      <c r="S10" s="20">
         <v>8.9652028567087072</v>
       </c>
-      <c r="T10" s="26">
+      <c r="T10" s="20">
         <v>8.7918321043675558</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="U10" s="20">
+        <v>5.5072463768115947</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="19">
         <v>17.491993101749202</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="19">
         <v>13.82849531868218</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="19">
         <v>13.109231388919405</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="19">
         <v>11.416709911779968</v>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="19">
         <v>11.646040014599025</v>
       </c>
-      <c r="I11" s="25">
+      <c r="I11" s="19">
         <v>11.539978958442925</v>
       </c>
-      <c r="J11" s="25">
+      <c r="J11" s="19">
         <v>13.183481098183975</v>
       </c>
-      <c r="K11" s="25">
+      <c r="K11" s="19">
         <v>14.415325767394808</v>
       </c>
-      <c r="L11" s="25">
+      <c r="L11" s="19">
         <v>12.659814489847079</v>
       </c>
-      <c r="M11" s="25">
+      <c r="M11" s="19">
         <v>11.493097440021446</v>
       </c>
-      <c r="N11" s="25">
+      <c r="N11" s="19">
         <v>9.9185738699192445</v>
       </c>
-      <c r="O11" s="25">
+      <c r="O11" s="19">
         <v>10.180383673209684</v>
       </c>
-      <c r="P11" s="25">
+      <c r="P11" s="19">
         <v>9.5190846795448198</v>
       </c>
-      <c r="Q11" s="25">
+      <c r="Q11" s="19">
         <v>8.6999999999999993</v>
       </c>
-      <c r="R11" s="25">
+      <c r="R11" s="19">
         <v>10.199999999999999</v>
       </c>
-      <c r="S11" s="25">
+      <c r="S11" s="19">
         <v>8.5830821067565175</v>
       </c>
-      <c r="T11" s="25">
+      <c r="T11" s="19">
         <v>6.8097801413840067</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="U11" s="19">
+        <v>8.4600087633556917</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="20">
         <v>19.421323820848194</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="20">
         <v>15.741380634262457</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="20">
         <v>14.475185396463205</v>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="20">
         <v>12.663343661592348</v>
       </c>
-      <c r="H12" s="26">
+      <c r="H12" s="20">
         <v>13.039247486214725</v>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="20">
         <v>13.211903540277065</v>
       </c>
-      <c r="J12" s="26">
+      <c r="J12" s="20">
         <v>13.028055465978715</v>
       </c>
-      <c r="K12" s="26">
+      <c r="K12" s="20">
         <v>15.585048094484353</v>
       </c>
-      <c r="L12" s="26">
+      <c r="L12" s="20">
         <v>13.350171387335378</v>
       </c>
-      <c r="M12" s="26">
+      <c r="M12" s="20">
         <v>11.935820506130968</v>
       </c>
-      <c r="N12" s="26">
+      <c r="N12" s="20">
         <v>10.467459853065471</v>
       </c>
-      <c r="O12" s="26">
+      <c r="O12" s="20">
         <v>10.48777460593273</v>
       </c>
-      <c r="P12" s="26">
+      <c r="P12" s="20">
         <v>9.9217353793060941</v>
       </c>
-      <c r="Q12" s="26">
+      <c r="Q12" s="20">
         <v>8.8000000000000007</v>
       </c>
-      <c r="R12" s="26">
+      <c r="R12" s="20">
         <v>10.5</v>
       </c>
-      <c r="S12" s="26">
+      <c r="S12" s="20">
         <v>10.275380189066995</v>
       </c>
-      <c r="T12" s="26">
+      <c r="T12" s="20">
         <v>7.8495916946255617</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
+      <c r="U12" s="20">
+        <v>10.108966784823423</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="20">
         <v>15.418689837294488</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="20">
         <v>11.836212412028152</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="20">
         <v>11.667293940534437</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="20">
         <v>10.10029162813856</v>
       </c>
-      <c r="H13" s="26">
+      <c r="H13" s="20">
         <v>10.187449062754686</v>
       </c>
-      <c r="I13" s="26">
+      <c r="I13" s="20">
         <v>9.78143550998381</v>
       </c>
-      <c r="J13" s="26">
+      <c r="J13" s="20">
         <v>13.34591534106228</v>
       </c>
-      <c r="K13" s="26">
+      <c r="K13" s="20">
         <v>13.151837969356219</v>
       </c>
-      <c r="L13" s="26">
+      <c r="L13" s="20">
         <v>11.908656677353923</v>
       </c>
-      <c r="M13" s="26">
+      <c r="M13" s="20">
         <v>11.025358324145534</v>
       </c>
-      <c r="N13" s="26">
+      <c r="N13" s="20">
         <v>9.3348084635596731</v>
       </c>
-      <c r="O13" s="26">
+      <c r="O13" s="20">
         <v>9.8570402767804701</v>
       </c>
-      <c r="P13" s="26">
+      <c r="P13" s="20">
         <v>9.1113330004992505</v>
       </c>
-      <c r="Q13" s="26">
+      <c r="Q13" s="20">
         <v>8.6</v>
       </c>
-      <c r="R13" s="26">
+      <c r="R13" s="20">
         <v>10</v>
       </c>
-      <c r="S13" s="26">
+      <c r="S13" s="20">
         <v>6.7661984261234096</v>
       </c>
-      <c r="T13" s="26">
+      <c r="T13" s="20">
         <v>5.7177049398311288</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="U13" s="20">
+        <v>6.7197783165916176</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="19">
         <v>17.433751743375176</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="19">
         <v>18.441460185360317</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="19">
         <v>16.389013957676724</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="19">
         <v>15.933098591549296</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="19">
         <v>16.267429388630678</v>
       </c>
-      <c r="I14" s="25">
+      <c r="I14" s="19">
         <v>14.752650176678445</v>
       </c>
-      <c r="J14" s="25">
+      <c r="J14" s="19">
         <v>11.26105165193113</v>
       </c>
-      <c r="K14" s="25">
+      <c r="K14" s="19">
         <v>9.3061826223164097</v>
       </c>
-      <c r="L14" s="25">
+      <c r="L14" s="19">
         <v>12.182109194380224</v>
       </c>
-      <c r="M14" s="25">
+      <c r="M14" s="19">
         <v>8.4201388888888893</v>
       </c>
-      <c r="N14" s="25">
+      <c r="N14" s="19">
         <v>9.4235033259423506</v>
       </c>
-      <c r="O14" s="25">
+      <c r="O14" s="19">
         <v>8.4504536559331083</v>
       </c>
-      <c r="P14" s="25">
+      <c r="P14" s="19">
         <v>11.651037226484798</v>
       </c>
-      <c r="Q14" s="25">
+      <c r="Q14" s="19">
         <v>9.6999999999999993</v>
       </c>
-      <c r="R14" s="25">
+      <c r="R14" s="19">
         <v>19.399999999999999</v>
       </c>
-      <c r="S14" s="25">
+      <c r="S14" s="19">
         <v>9.0818473806623103</v>
       </c>
-      <c r="T14" s="25">
+      <c r="T14" s="19">
         <v>5.5726364335126828</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
+      <c r="U14" s="19">
+        <v>6.1859851941993718</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="20">
         <v>21.032132424537487</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="20">
         <v>22.853957636566332</v>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="20">
         <v>14.873746108612936</v>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="20">
         <v>19.34369602763385</v>
       </c>
-      <c r="H15" s="26">
+      <c r="H15" s="20">
         <v>19.604380077711056</v>
       </c>
-      <c r="I15" s="26">
+      <c r="I15" s="20">
         <v>15.392688472975337</v>
       </c>
-      <c r="J15" s="26">
+      <c r="J15" s="20">
         <v>11.231884057971014</v>
       </c>
-      <c r="K15" s="26">
+      <c r="K15" s="20">
         <v>10.857763300760043</v>
       </c>
-      <c r="L15" s="26">
+      <c r="L15" s="20">
         <v>13.852813852813853</v>
       </c>
-      <c r="M15" s="26">
+      <c r="M15" s="20">
         <v>7.3781743308167469</v>
       </c>
-      <c r="N15" s="26">
+      <c r="N15" s="20">
         <v>11.22216377345257</v>
       </c>
-      <c r="O15" s="26">
+      <c r="O15" s="20">
         <v>8.9129674938832579</v>
       </c>
-      <c r="P15" s="29">
+      <c r="P15" s="20">
         <v>13.681138270704123</v>
       </c>
-      <c r="Q15" s="26">
+      <c r="Q15" s="20">
         <v>10.5</v>
       </c>
-      <c r="R15" s="26">
+      <c r="R15" s="20">
         <v>22.3</v>
       </c>
-      <c r="S15" s="26">
+      <c r="S15" s="20">
         <v>9.0186815546489161</v>
       </c>
-      <c r="T15" s="26">
+      <c r="T15" s="20">
         <v>5.8888479941111518</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
+      <c r="U15" s="20">
+        <v>7.4282272636016868</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="20">
         <v>13.665102998164389</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="20">
         <v>13.86748844375963</v>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="20">
         <v>18.034942701484127</v>
       </c>
-      <c r="G16" s="26">
+      <c r="G16" s="20">
         <v>12.387791741472173</v>
       </c>
-      <c r="H16" s="26">
+      <c r="H16" s="20">
         <v>12.848353239232718</v>
       </c>
-      <c r="I16" s="26">
+      <c r="I16" s="20">
         <v>14.099589505621989</v>
       </c>
-      <c r="J16" s="26">
+      <c r="J16" s="20">
         <v>11.291866028708133</v>
       </c>
-      <c r="K16" s="26">
+      <c r="K16" s="20">
         <v>7.6966397597146612</v>
       </c>
-      <c r="L16" s="26">
+      <c r="L16" s="20">
         <v>10.418570645220253</v>
       </c>
-      <c r="M16" s="26">
+      <c r="M16" s="20">
         <v>9.4869992972593113</v>
       </c>
-      <c r="N16" s="26">
+      <c r="N16" s="20">
         <v>7.4204256981058387</v>
       </c>
-      <c r="O16" s="26">
+      <c r="O16" s="20">
         <v>7.9710144927536231</v>
       </c>
-      <c r="P16" s="26">
+      <c r="P16" s="20">
         <v>9.4581280788177331</v>
       </c>
-      <c r="Q16" s="26">
+      <c r="Q16" s="20">
         <v>8.6999999999999993</v>
       </c>
-      <c r="R16" s="26">
+      <c r="R16" s="20">
         <v>16.399999999999999</v>
       </c>
-      <c r="S16" s="26">
+      <c r="S16" s="20">
         <v>9.149130832570906</v>
       </c>
-      <c r="T16" s="26">
+      <c r="T16" s="20">
         <v>5.2271813429835143</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+      <c r="U16" s="20">
+        <v>4.918032786885246</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="19">
         <v>17.912772585669781</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="19">
         <v>16.943930991990143</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="19">
         <v>14.464366430616241</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="19">
         <v>12.251148545176111</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="19">
         <v>10.273497153963627</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="19">
         <v>12.369974697779028</v>
       </c>
-      <c r="J17" s="25">
+      <c r="J17" s="19">
         <v>11.584129742253113</v>
       </c>
-      <c r="K17" s="25">
+      <c r="K17" s="19">
         <v>12.209828157974075</v>
       </c>
-      <c r="L17" s="25">
+      <c r="L17" s="19">
         <v>8.720930232558139</v>
       </c>
-      <c r="M17" s="25">
+      <c r="M17" s="19">
         <v>11.227763196267134</v>
       </c>
-      <c r="N17" s="25">
+      <c r="N17" s="19">
         <v>9.9843993759750393</v>
       </c>
-      <c r="O17" s="25">
+      <c r="O17" s="19">
         <v>8.1546360616128055</v>
       </c>
-      <c r="P17" s="25">
+      <c r="P17" s="19">
         <v>6.6291017567119654</v>
       </c>
-      <c r="Q17" s="25">
+      <c r="Q17" s="19">
         <v>9.6</v>
       </c>
-      <c r="R17" s="25">
+      <c r="R17" s="19">
         <v>9.4</v>
       </c>
-      <c r="S17" s="25">
+      <c r="S17" s="19">
         <v>8.0270384452893957</v>
       </c>
-      <c r="T17" s="25">
+      <c r="T17" s="19">
         <v>4.9464138499587795</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
+      <c r="U17" s="19">
+        <v>3.044360684256306</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="20">
         <v>19.708914493632506</v>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="20">
         <v>17.851739788199698</v>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="20">
         <v>17.657445556209534</v>
       </c>
-      <c r="G18" s="26">
+      <c r="G18" s="20">
         <v>12.803050939798419</v>
       </c>
-      <c r="H18" s="26">
+      <c r="H18" s="20">
         <v>12.983500135244793</v>
       </c>
-      <c r="I18" s="26">
+      <c r="I18" s="20">
         <v>13.358778625954198</v>
       </c>
-      <c r="J18" s="26">
+      <c r="J18" s="20">
         <v>12.704686617730095</v>
       </c>
-      <c r="K18" s="26">
+      <c r="K18" s="20">
         <v>12.242460435951031</v>
       </c>
-      <c r="L18" s="26">
+      <c r="L18" s="20">
         <v>11.589895988112927</v>
       </c>
-      <c r="M18" s="26">
+      <c r="M18" s="20">
         <v>11.428571428571429</v>
       </c>
-      <c r="N18" s="26">
+      <c r="N18" s="20">
         <v>12.080942313500454</v>
       </c>
-      <c r="O18" s="26">
+      <c r="O18" s="20">
         <v>8.3160083160083165</v>
       </c>
-      <c r="P18" s="26">
+      <c r="P18" s="20">
         <v>7.5459317585301839</v>
       </c>
-      <c r="Q18" s="26">
+      <c r="Q18" s="20">
         <v>10.7</v>
       </c>
-      <c r="R18" s="26">
+      <c r="R18" s="20">
         <v>11.4</v>
       </c>
-      <c r="S18" s="26">
+      <c r="S18" s="20">
         <v>8.8235294117647065</v>
       </c>
-      <c r="T18" s="26">
+      <c r="T18" s="20">
         <v>5.8886509635974305</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
+      <c r="U18" s="20">
+        <v>2.785515320334262</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="20">
         <v>16.015374759769379</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="20">
         <v>16.002510197678067</v>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="20">
         <v>11.114541525162087</v>
       </c>
-      <c r="G19" s="26">
+      <c r="G19" s="20">
         <v>11.674259681093394</v>
       </c>
-      <c r="H19" s="26">
+      <c r="H19" s="20">
         <v>7.4158585282373073</v>
       </c>
-      <c r="I19" s="26">
+      <c r="I19" s="20">
         <v>11.317469529889728</v>
       </c>
-      <c r="J19" s="26">
+      <c r="J19" s="20">
         <v>10.404280618311534</v>
       </c>
-      <c r="K19" s="26">
+      <c r="K19" s="20">
         <v>12.176560121765601</v>
       </c>
-      <c r="L19" s="26">
+      <c r="L19" s="20">
         <v>5.6764427625354781</v>
       </c>
-      <c r="M19" s="26">
+      <c r="M19" s="20">
         <v>11.018463371054199</v>
       </c>
-      <c r="N19" s="26">
+      <c r="N19" s="20">
         <v>7.7444336882865441</v>
       </c>
-      <c r="O19" s="26">
+      <c r="O19" s="20">
         <v>7.9877112135176649</v>
       </c>
-      <c r="P19" s="26">
+      <c r="P19" s="20">
         <v>5.6932350971198922</v>
       </c>
-      <c r="Q19" s="26">
+      <c r="Q19" s="20">
         <v>8.6</v>
       </c>
-      <c r="R19" s="26">
+      <c r="R19" s="20">
         <v>7.3</v>
       </c>
-      <c r="S19" s="26">
+      <c r="S19" s="20">
         <v>7.2217502124044177</v>
       </c>
-      <c r="T19" s="26">
+      <c r="T19" s="20">
         <v>3.9525691699604741</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+      <c r="U19" s="20">
+        <v>3.3252720677146308</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="19">
         <v>12.608002373271036</v>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="19">
         <v>13.417951042611062</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="19">
         <v>10.630954024575452</v>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="19">
         <v>10.695523608795495</v>
       </c>
-      <c r="H20" s="25">
+      <c r="H20" s="19">
         <v>8.2142857142857135</v>
       </c>
-      <c r="I20" s="25">
+      <c r="I20" s="19">
         <v>6.4441219158200287</v>
       </c>
-      <c r="J20" s="25">
+      <c r="J20" s="19">
         <v>5.1059702769774935</v>
       </c>
-      <c r="K20" s="25">
+      <c r="K20" s="19">
         <v>5.0451623403043371</v>
       </c>
-      <c r="L20" s="25">
+      <c r="L20" s="19">
         <v>4.3125446565275087</v>
       </c>
-      <c r="M20" s="25">
+      <c r="M20" s="19">
         <v>3.4859593304744778</v>
       </c>
-      <c r="N20" s="25">
+      <c r="N20" s="19">
         <v>3.0982632671044028</v>
       </c>
-      <c r="O20" s="25">
+      <c r="O20" s="19">
         <v>3.3626990523302669</v>
       </c>
-      <c r="P20" s="25">
+      <c r="P20" s="19">
         <v>2.8324599915026201</v>
       </c>
-      <c r="Q20" s="25">
+      <c r="Q20" s="19">
         <v>3.9</v>
       </c>
-      <c r="R20" s="25">
+      <c r="R20" s="19">
         <v>3.1</v>
       </c>
-      <c r="S20" s="25">
+      <c r="S20" s="19">
         <v>3.4213262670647033</v>
       </c>
-      <c r="T20" s="25">
+      <c r="T20" s="19">
         <v>1.7935943060498221</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
+      <c r="U20" s="19">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="20" t="s">
+      <c r="B21" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="20">
         <v>12.992637505413599</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="20">
         <v>14.691547138281576</v>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="20">
         <v>12.544204977647295</v>
       </c>
-      <c r="G21" s="26">
+      <c r="G21" s="20">
         <v>12.92517006802721</v>
       </c>
-      <c r="H21" s="26">
+      <c r="H21" s="20">
         <v>9.3290068374087394</v>
       </c>
-      <c r="I21" s="26">
+      <c r="I21" s="20">
         <v>7.0335358991672292</v>
       </c>
-      <c r="J21" s="26">
+      <c r="J21" s="20">
         <v>5.5116356753145528</v>
       </c>
-      <c r="K21" s="26">
+      <c r="K21" s="20">
         <v>5.4454136928363726</v>
       </c>
-      <c r="L21" s="26">
+      <c r="L21" s="20">
         <v>5.1058717525153927</v>
       </c>
-      <c r="M21" s="26">
+      <c r="M21" s="20">
         <v>3.852739726027397</v>
       </c>
-      <c r="N21" s="26">
+      <c r="N21" s="20">
         <v>3.4500027822603085</v>
       </c>
-      <c r="O21" s="26">
+      <c r="O21" s="20">
         <v>4.0540540540540544</v>
       </c>
-      <c r="P21" s="26">
+      <c r="P21" s="20">
         <v>3.4114669307802354</v>
       </c>
-      <c r="Q21" s="26">
+      <c r="Q21" s="20">
         <v>4.0999999999999996</v>
       </c>
-      <c r="R21" s="26">
+      <c r="R21" s="20">
         <v>2.9</v>
       </c>
-      <c r="S21" s="26">
+      <c r="S21" s="20">
         <v>3.4802022457154114</v>
       </c>
-      <c r="T21" s="26">
+      <c r="T21" s="20">
         <v>2.2260559853080308</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="U21" s="20">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="20">
         <v>12.201631968275757</v>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="20">
         <v>12.033603269507305</v>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="20">
         <v>8.5806220951018943</v>
       </c>
-      <c r="G22" s="26">
+      <c r="G22" s="20">
         <v>8.3872206927460144</v>
       </c>
-      <c r="H22" s="26">
+      <c r="H22" s="20">
         <v>7.0370823644596747</v>
       </c>
-      <c r="I22" s="26">
+      <c r="I22" s="20">
         <v>5.8160450893392497</v>
       </c>
-      <c r="J22" s="26">
+      <c r="J22" s="20">
         <v>4.6797309154723603</v>
       </c>
-      <c r="K22" s="26">
+      <c r="K22" s="20">
         <v>4.6234402852049907</v>
       </c>
-      <c r="L22" s="26">
+      <c r="L22" s="20">
         <v>3.4875852376242782</v>
       </c>
-      <c r="M22" s="26">
+      <c r="M22" s="20">
         <v>3.0933150025777625</v>
       </c>
-      <c r="N22" s="26">
+      <c r="N22" s="20">
         <v>2.7309703660662406</v>
       </c>
-      <c r="O22" s="26">
+      <c r="O22" s="20">
         <v>2.6311273808842879</v>
       </c>
-      <c r="P22" s="26">
+      <c r="P22" s="20">
         <v>2.218200922304594</v>
       </c>
-      <c r="Q22" s="26">
+      <c r="Q22" s="20">
         <v>3.6</v>
       </c>
-      <c r="R22" s="26">
+      <c r="R22" s="20">
         <v>3.4</v>
       </c>
-      <c r="S22" s="26">
+      <c r="S22" s="20">
         <v>3.3598464070213931</v>
       </c>
-      <c r="T22" s="26">
+      <c r="T22" s="20">
         <v>1.3406388435532757</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+      <c r="U22" s="20">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="25">
+      <c r="D23" s="19">
         <v>28.861020443222813</v>
       </c>
-      <c r="E23" s="25">
+      <c r="E23" s="19">
         <v>24.548244118649848</v>
       </c>
-      <c r="F23" s="25">
+      <c r="F23" s="19">
         <v>25.589947900704875</v>
       </c>
-      <c r="G23" s="25">
+      <c r="G23" s="19">
         <v>19.147084421235856</v>
       </c>
-      <c r="H23" s="25">
+      <c r="H23" s="19">
         <v>16.905248807089301</v>
       </c>
-      <c r="I23" s="25">
+      <c r="I23" s="19">
         <v>15.341308937368051</v>
       </c>
-      <c r="J23" s="25">
+      <c r="J23" s="19">
         <v>19.851851851851855</v>
       </c>
-      <c r="K23" s="25">
+      <c r="K23" s="19">
         <v>16.656751933372991</v>
       </c>
-      <c r="L23" s="25">
+      <c r="L23" s="19">
         <v>12.700332627759298</v>
       </c>
-      <c r="M23" s="25">
+      <c r="M23" s="19">
         <v>12.336039975015614</v>
       </c>
-      <c r="N23" s="25">
+      <c r="N23" s="19">
         <v>12.26790450928382</v>
       </c>
-      <c r="O23" s="25">
+      <c r="O23" s="19">
         <v>16.684858880399187</v>
       </c>
-      <c r="P23" s="25">
+      <c r="P23" s="19">
         <v>14.816047944065257</v>
       </c>
-      <c r="Q23" s="25">
+      <c r="Q23" s="19">
         <v>20.6</v>
       </c>
-      <c r="R23" s="25">
+      <c r="R23" s="19">
         <v>15</v>
       </c>
-      <c r="S23" s="25">
+      <c r="S23" s="19">
         <v>12.808072967203572</v>
       </c>
-      <c r="T23" s="25">
+      <c r="T23" s="19">
         <v>9.113100081366964</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
+      <c r="U23" s="19">
+        <v>7.7423895829667435</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="20">
         <v>32.937181663837009</v>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="20">
         <v>26.245847176079732</v>
       </c>
-      <c r="F24" s="26">
+      <c r="F24" s="20">
         <v>28.698224852071004</v>
       </c>
-      <c r="G24" s="26">
+      <c r="G24" s="20">
         <v>22.151898734177216</v>
       </c>
-      <c r="H24" s="26">
+      <c r="H24" s="20">
         <v>19.295958279009128</v>
       </c>
-      <c r="I24" s="26">
+      <c r="I24" s="20">
         <v>17.127071823204417</v>
       </c>
-      <c r="J24" s="26">
+      <c r="J24" s="20">
         <v>23.941605839416059</v>
       </c>
-      <c r="K24" s="26">
+      <c r="K24" s="20">
         <v>19.312695257029254</v>
       </c>
-      <c r="L24" s="26">
+      <c r="L24" s="20">
         <v>17.266608135791632</v>
       </c>
-      <c r="M24" s="26">
+      <c r="M24" s="20">
         <v>11.342734518700183</v>
       </c>
-      <c r="N24" s="26">
+      <c r="N24" s="20">
         <v>12.442698100851343</v>
       </c>
-      <c r="O24" s="26">
+      <c r="O24" s="20">
         <v>19.476567255021301</v>
       </c>
-      <c r="P24" s="26">
+      <c r="P24" s="20">
         <v>14.964216005204944</v>
       </c>
-      <c r="Q24" s="26">
+      <c r="Q24" s="20">
         <v>23.6</v>
       </c>
-      <c r="R24" s="26">
+      <c r="R24" s="20">
         <v>17.3</v>
       </c>
-      <c r="S24" s="26">
+      <c r="S24" s="20">
         <v>14.988470407378941</v>
       </c>
-      <c r="T24" s="26">
+      <c r="T24" s="20">
         <v>8.777633289986996</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
+      <c r="U24" s="20">
+        <v>9.2807424593967518</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c r="B25" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="20">
         <v>24.687065368567456</v>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="20">
         <v>22.75910364145658</v>
       </c>
-      <c r="F25" s="26">
+      <c r="F25" s="20">
         <v>22.250476795931341</v>
       </c>
-      <c r="G25" s="26">
+      <c r="G25" s="20">
         <v>16.091281451141018</v>
       </c>
-      <c r="H25" s="26">
+      <c r="H25" s="20">
         <v>14.285714285714285</v>
       </c>
-      <c r="I25" s="26">
+      <c r="I25" s="20">
         <v>13.486370157819225</v>
       </c>
-      <c r="J25" s="26">
+      <c r="J25" s="20">
         <v>15.639097744360903</v>
       </c>
-      <c r="K25" s="26">
+      <c r="K25" s="20">
         <v>13.737121448641897</v>
       </c>
-      <c r="L25" s="26">
+      <c r="L25" s="20">
         <v>7.8198310916484211</v>
       </c>
-      <c r="M25" s="26">
+      <c r="M25" s="20">
         <v>13.367281985996181</v>
       </c>
-      <c r="N25" s="26">
+      <c r="N25" s="20">
         <v>12.08865010073875</v>
       </c>
-      <c r="O25" s="26">
+      <c r="O25" s="20">
         <v>13.751199232491205</v>
       </c>
-      <c r="P25" s="26">
+      <c r="P25" s="20">
         <v>14.660756904193658</v>
       </c>
-      <c r="Q25" s="26">
+      <c r="Q25" s="20">
         <v>17.5</v>
       </c>
-      <c r="R25" s="26">
+      <c r="R25" s="20">
         <v>12.7</v>
       </c>
-      <c r="S25" s="26">
+      <c r="S25" s="20">
         <v>10.584084672677381</v>
       </c>
-      <c r="T25" s="26">
+      <c r="T25" s="20">
         <v>9.4493320299771923</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+      <c r="U25" s="20">
+        <v>6.0015003750937739</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="25">
+      <c r="D26" s="19">
         <v>21.918468115854761</v>
       </c>
-      <c r="E26" s="25">
+      <c r="E26" s="19">
         <v>19.965576592082616</v>
       </c>
-      <c r="F26" s="25">
+      <c r="F26" s="19">
         <v>18.539076376554174</v>
       </c>
-      <c r="G26" s="25">
+      <c r="G26" s="19">
         <v>16.072399980218584</v>
       </c>
-      <c r="H26" s="25">
+      <c r="H26" s="19">
         <v>15.374759769378604</v>
       </c>
-      <c r="I26" s="25">
+      <c r="I26" s="19">
         <v>14.294877668835333</v>
       </c>
-      <c r="J26" s="25">
+      <c r="J26" s="19">
         <v>14.537283316518389</v>
       </c>
-      <c r="K26" s="25">
+      <c r="K26" s="19">
         <v>13.354037267080745</v>
       </c>
-      <c r="L26" s="25">
+      <c r="L26" s="19">
         <v>12.614627600089467</v>
       </c>
-      <c r="M26" s="25">
+      <c r="M26" s="19">
         <v>10.40759449573245</v>
       </c>
-      <c r="N26" s="25">
+      <c r="N26" s="19">
         <v>6.6553449304631203</v>
       </c>
-      <c r="O26" s="25">
+      <c r="O26" s="19">
         <v>6.8021734755484005</v>
       </c>
-      <c r="P26" s="25">
+      <c r="P26" s="19">
         <v>7.5963764877929885</v>
       </c>
-      <c r="Q26" s="25">
+      <c r="Q26" s="19">
         <v>6.9</v>
       </c>
-      <c r="R26" s="25">
+      <c r="R26" s="19">
         <v>7.9</v>
       </c>
-      <c r="S26" s="25">
+      <c r="S26" s="19">
         <v>7.1442946266854497</v>
       </c>
-      <c r="T26" s="25">
+      <c r="T26" s="19">
         <v>4.753114905399169</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
+      <c r="U26" s="19">
+        <v>2.3406152474364692</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="20" t="s">
+      <c r="B27" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="26">
+      <c r="D27" s="20">
         <v>23.945800724214461</v>
       </c>
-      <c r="E27" s="26">
+      <c r="E27" s="20">
         <v>24.466540051390908</v>
       </c>
-      <c r="F27" s="26">
+      <c r="F27" s="20">
         <v>20.4257149000215</v>
       </c>
-      <c r="G27" s="26">
+      <c r="G27" s="20">
         <v>18.399616674652613</v>
       </c>
-      <c r="H27" s="26">
+      <c r="H27" s="20">
         <v>14.611960518676215</v>
       </c>
-      <c r="I27" s="26">
+      <c r="I27" s="20">
         <v>16.048502139800284</v>
       </c>
-      <c r="J27" s="26">
+      <c r="J27" s="20">
         <v>16.233478222301073</v>
       </c>
-      <c r="K27" s="26">
+      <c r="K27" s="20">
         <v>13.94180810529962</v>
       </c>
-      <c r="L27" s="26">
+      <c r="L27" s="20">
         <v>14.593527341402696</v>
       </c>
-      <c r="M27" s="26">
+      <c r="M27" s="20">
         <v>11.048784633690294</v>
       </c>
-      <c r="N27" s="26">
+      <c r="N27" s="20">
         <v>6.8057669920300885</v>
       </c>
-      <c r="O27" s="26">
+      <c r="O27" s="20">
         <v>7.498618675507144</v>
       </c>
-      <c r="P27" s="26">
+      <c r="P27" s="20">
         <v>8.2226438962681847</v>
       </c>
-      <c r="Q27" s="26">
+      <c r="Q27" s="20">
         <v>7.8</v>
       </c>
-      <c r="R27" s="26">
+      <c r="R27" s="20">
         <v>8.4</v>
       </c>
-      <c r="S27" s="26">
+      <c r="S27" s="20">
         <v>7.5305623471882646</v>
       </c>
-      <c r="T27" s="26">
+      <c r="T27" s="20">
         <v>5.1499819298879652</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
+      <c r="U27" s="20">
+        <v>2.2656165713669218</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="20" t="s">
+      <c r="B28" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="26">
+      <c r="D28" s="20">
         <v>19.7613721103654</v>
       </c>
-      <c r="E28" s="26">
+      <c r="E28" s="20">
         <v>15.214058261587452</v>
       </c>
-      <c r="F28" s="26">
+      <c r="F28" s="20">
         <v>16.525131971540052</v>
       </c>
-      <c r="G28" s="26">
+      <c r="G28" s="20">
         <v>13.590844062947067</v>
       </c>
-      <c r="H28" s="26">
+      <c r="H28" s="20">
         <v>16.166281755196305</v>
       </c>
-      <c r="I28" s="26">
+      <c r="I28" s="20">
         <v>12.441093308199811</v>
       </c>
-      <c r="J28" s="26">
+      <c r="J28" s="20">
         <v>12.721921579796829</v>
       </c>
-      <c r="K28" s="26">
+      <c r="K28" s="20">
         <v>12.736535662299854</v>
       </c>
-      <c r="L28" s="26">
+      <c r="L28" s="20">
         <v>10.461423500840649</v>
       </c>
-      <c r="M28" s="26">
+      <c r="M28" s="20">
         <v>9.7338810501875326</v>
       </c>
-      <c r="N28" s="26">
+      <c r="N28" s="20">
         <v>6.4971751412429377</v>
       </c>
-      <c r="O28" s="26">
+      <c r="O28" s="20">
         <v>6.0775295663600524</v>
       </c>
-      <c r="P28" s="26">
+      <c r="P28" s="20">
         <v>6.9345810009190405</v>
       </c>
-      <c r="Q28" s="26">
+      <c r="Q28" s="20">
         <v>5.9</v>
       </c>
-      <c r="R28" s="26">
+      <c r="R28" s="20">
         <v>7.4</v>
       </c>
-      <c r="S28" s="26">
+      <c r="S28" s="20">
         <v>6.7350533623458704</v>
       </c>
-      <c r="T28" s="26">
+      <c r="T28" s="20">
         <v>4.3388039992454255</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="35" t="s">
+      <c r="U28" s="20">
+        <v>2.4207492795389047</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="25">
+      <c r="D29" s="19">
         <v>31.519613482112046</v>
       </c>
-      <c r="E29" s="25">
+      <c r="E29" s="19">
         <v>29.874559859154928</v>
       </c>
-      <c r="F29" s="25">
+      <c r="F29" s="19">
         <v>27.261588727792528</v>
       </c>
-      <c r="G29" s="25">
+      <c r="G29" s="19">
         <v>25.128553410303677</v>
       </c>
-      <c r="H29" s="25">
+      <c r="H29" s="19">
         <v>24.125336409073434</v>
       </c>
-      <c r="I29" s="25">
+      <c r="I29" s="19">
         <v>21.386530080424137</v>
       </c>
-      <c r="J29" s="25">
+      <c r="J29" s="19">
         <v>22.85490400940316</v>
       </c>
-      <c r="K29" s="25">
+      <c r="K29" s="19">
         <v>25.985736535781623</v>
       </c>
-      <c r="L29" s="25">
+      <c r="L29" s="19">
         <v>23.028611304954641</v>
       </c>
-      <c r="M29" s="25">
+      <c r="M29" s="19">
         <v>22.846557579499844</v>
       </c>
-      <c r="N29" s="25">
+      <c r="N29" s="19">
         <v>23.162225004471473</v>
       </c>
-      <c r="O29" s="25">
+      <c r="O29" s="19">
         <v>22.937930537021675</v>
       </c>
-      <c r="P29" s="25">
+      <c r="P29" s="19">
         <v>19.881856540084385</v>
       </c>
-      <c r="Q29" s="25">
+      <c r="Q29" s="19">
         <v>19</v>
       </c>
-      <c r="R29" s="25">
+      <c r="R29" s="19">
         <v>15.2</v>
       </c>
-      <c r="S29" s="25">
+      <c r="S29" s="19">
         <v>16.241806263656226</v>
       </c>
-      <c r="T29" s="25">
+      <c r="T29" s="19">
         <v>40.755007704160249</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
+      <c r="U29" s="19">
+        <v>28.194893239561555</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="20" t="s">
+      <c r="B30" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="26">
+      <c r="D30" s="20">
         <v>32.360262502828697</v>
       </c>
-      <c r="E30" s="26">
+      <c r="E30" s="20">
         <v>33.077004108290325</v>
       </c>
-      <c r="F30" s="26">
+      <c r="F30" s="20">
         <v>29.476418864908073</v>
       </c>
-      <c r="G30" s="26">
+      <c r="G30" s="20">
         <v>25.65795679652863</v>
       </c>
-      <c r="H30" s="26">
+      <c r="H30" s="20">
         <v>25.966747618158045</v>
       </c>
-      <c r="I30" s="26">
+      <c r="I30" s="20">
         <v>22.187281621243887</v>
       </c>
-      <c r="J30" s="26">
+      <c r="J30" s="20">
         <v>26.051421760599354</v>
       </c>
-      <c r="K30" s="26">
+      <c r="K30" s="20">
         <v>27.5571791613723</v>
       </c>
-      <c r="L30" s="26">
+      <c r="L30" s="20">
         <v>24.59901936341727</v>
       </c>
-      <c r="M30" s="26">
+      <c r="M30" s="20">
         <v>25.325119780971935</v>
       </c>
-      <c r="N30" s="26">
+      <c r="N30" s="20">
         <v>25.97516179814588</v>
       </c>
-      <c r="O30" s="26">
+      <c r="O30" s="20">
         <v>25.00174593197849</v>
       </c>
-      <c r="P30" s="26">
+      <c r="P30" s="20">
         <v>21.589793915603533</v>
       </c>
-      <c r="Q30" s="26">
+      <c r="Q30" s="20">
         <v>19.7</v>
       </c>
-      <c r="R30" s="26">
+      <c r="R30" s="20">
         <v>17.600000000000001</v>
       </c>
-      <c r="S30" s="26">
+      <c r="S30" s="20">
         <v>15.614010409340272</v>
       </c>
-      <c r="T30" s="26">
+      <c r="T30" s="20">
         <v>39.809154614581779</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
+      <c r="U30" s="20">
+        <v>26.639108967734526</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="20" t="s">
+      <c r="B31" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="26">
+      <c r="D31" s="20">
         <v>30.650444548432382</v>
       </c>
-      <c r="E31" s="26">
+      <c r="E31" s="20">
         <v>26.373373258090524</v>
       </c>
-      <c r="F31" s="26">
+      <c r="F31" s="20">
         <v>24.947807933194152</v>
       </c>
-      <c r="G31" s="26">
+      <c r="G31" s="20">
         <v>24.568061520023971</v>
       </c>
-      <c r="H31" s="26">
+      <c r="H31" s="20">
         <v>22.173826964957435</v>
       </c>
-      <c r="I31" s="26">
+      <c r="I31" s="20">
         <v>20.538440188731613</v>
       </c>
-      <c r="J31" s="26">
+      <c r="J31" s="20">
         <v>19.510022271714924</v>
       </c>
-      <c r="K31" s="26">
+      <c r="K31" s="20">
         <v>24.309673047602914</v>
       </c>
-      <c r="L31" s="26">
+      <c r="L31" s="20">
         <v>21.294171638366223</v>
       </c>
-      <c r="M31" s="26">
+      <c r="M31" s="20">
         <v>20.209376422394172</v>
       </c>
-      <c r="N31" s="26">
+      <c r="N31" s="20">
         <v>20.2195791399817</v>
       </c>
-      <c r="O31" s="26">
+      <c r="O31" s="20">
         <v>20.733890214797135</v>
       </c>
-      <c r="P31" s="26">
+      <c r="P31" s="20">
         <v>18.061366806136682</v>
       </c>
-      <c r="Q31" s="26">
+      <c r="Q31" s="20">
         <v>18.399999999999999</v>
       </c>
-      <c r="R31" s="26">
+      <c r="R31" s="20">
         <v>12.6</v>
       </c>
-      <c r="S31" s="26">
+      <c r="S31" s="20">
         <v>16.915873735085334</v>
       </c>
-      <c r="T31" s="26">
+      <c r="T31" s="20">
         <v>41.76630001594134</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="35" t="s">
+      <c r="U31" s="20">
+        <v>30.110262934690414</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D32" s="25">
+      <c r="D32" s="19">
         <v>49.506943046890726</v>
       </c>
-      <c r="E32" s="25">
+      <c r="E32" s="19">
         <v>42.992095623674572</v>
       </c>
-      <c r="F32" s="25">
+      <c r="F32" s="19">
         <v>49.784765113232268</v>
       </c>
-      <c r="G32" s="25">
+      <c r="G32" s="19">
         <v>42.065009560229448</v>
       </c>
-      <c r="H32" s="25">
+      <c r="H32" s="19">
         <v>46.632124352331608</v>
       </c>
-      <c r="I32" s="25">
+      <c r="I32" s="19">
         <v>53.846153846153847</v>
       </c>
-      <c r="J32" s="25">
+      <c r="J32" s="19">
         <v>55.639097744360903</v>
       </c>
-      <c r="K32" s="25">
+      <c r="K32" s="19">
         <v>63.961300725611387</v>
       </c>
-      <c r="L32" s="25">
+      <c r="L32" s="19">
         <v>61.96377502383222</v>
       </c>
-      <c r="M32" s="25">
+      <c r="M32" s="19">
         <v>50.222162380503569</v>
       </c>
-      <c r="N32" s="25">
+      <c r="N32" s="19">
         <v>46.86485784759185</v>
       </c>
-      <c r="O32" s="25">
+      <c r="O32" s="19">
         <v>34.244292617897017</v>
       </c>
-      <c r="P32" s="25">
+      <c r="P32" s="19">
         <v>32.995296884185777</v>
       </c>
-      <c r="Q32" s="25">
+      <c r="Q32" s="19">
         <v>32.9</v>
       </c>
-      <c r="R32" s="25">
+      <c r="R32" s="19">
         <v>27.9</v>
       </c>
-      <c r="S32" s="25">
+      <c r="S32" s="19">
         <v>22.910065805508165</v>
       </c>
-      <c r="T32" s="25">
+      <c r="T32" s="19">
         <v>57.518248175182478</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
+      <c r="U32" s="19">
+        <v>40.629095674967232</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="20" t="s">
+      <c r="B33" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="30" t="s">
+      <c r="C33" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D33" s="26">
+      <c r="D33" s="20">
         <v>52.108194112967382</v>
       </c>
-      <c r="E33" s="26">
+      <c r="E33" s="20">
         <v>46.096654275092938</v>
       </c>
-      <c r="F33" s="26">
+      <c r="F33" s="20">
         <v>55.092424791591156</v>
       </c>
-      <c r="G33" s="26">
+      <c r="G33" s="20">
         <v>46.169287387085987</v>
       </c>
-      <c r="H33" s="26">
+      <c r="H33" s="20">
         <v>50.086355785837654</v>
       </c>
-      <c r="I33" s="26">
+      <c r="I33" s="20">
         <v>61.253972840219589</v>
       </c>
-      <c r="J33" s="26">
+      <c r="J33" s="20">
         <v>64.835787089467715</v>
       </c>
-      <c r="K33" s="26">
+      <c r="K33" s="20">
         <v>67.427385892116178</v>
       </c>
-      <c r="L33" s="26">
+      <c r="L33" s="20">
         <v>62.759336099585063</v>
       </c>
-      <c r="M33" s="26">
+      <c r="M33" s="20">
         <v>55.052985267510984</v>
       </c>
-      <c r="N33" s="26">
+      <c r="N33" s="20">
         <v>53.086419753086425</v>
       </c>
-      <c r="O33" s="26">
+      <c r="O33" s="20">
         <v>38.695235049568275</v>
       </c>
-      <c r="P33" s="26">
+      <c r="P33" s="20">
         <v>37.349742415569551</v>
       </c>
-      <c r="Q33" s="26">
+      <c r="Q33" s="20">
         <v>35.5</v>
       </c>
-      <c r="R33" s="26">
+      <c r="R33" s="20">
         <v>32.700000000000003</v>
       </c>
-      <c r="S33" s="26">
+      <c r="S33" s="20">
         <v>24.889729048519218</v>
       </c>
-      <c r="T33" s="26">
+      <c r="T33" s="20">
         <v>66.761768901569198</v>
       </c>
-    </row>
-    <row r="34" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="12" t="s">
+      <c r="U33" s="20">
+        <v>46.003815984736057</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="22" t="s">
+      <c r="B34" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="31" t="s">
+      <c r="C34" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="21">
         <v>46.843177189409367</v>
       </c>
-      <c r="E34" s="27">
+      <c r="E34" s="21">
         <v>39.647577092511014</v>
       </c>
-      <c r="F34" s="27">
+      <c r="F34" s="21">
         <v>44.117647058823529</v>
       </c>
-      <c r="G34" s="27">
+      <c r="G34" s="21">
         <v>37.626628075253258</v>
       </c>
-      <c r="H34" s="27">
+      <c r="H34" s="21">
         <v>42.931162102146558</v>
       </c>
-      <c r="I34" s="27">
+      <c r="I34" s="21">
         <v>45.755758914484062</v>
       </c>
-      <c r="J34" s="27">
+      <c r="J34" s="21">
         <v>45.221295702373311</v>
       </c>
-      <c r="K34" s="27">
+      <c r="K34" s="21">
         <v>60.234244283324038</v>
       </c>
-      <c r="L34" s="27">
+      <c r="L34" s="21">
         <v>61.084026383710921</v>
       </c>
-      <c r="M34" s="27">
+      <c r="M34" s="21">
         <v>44.969083754918493</v>
       </c>
-      <c r="N34" s="27">
+      <c r="N34" s="21">
         <v>39.967150287434983</v>
       </c>
-      <c r="O34" s="27">
+      <c r="O34" s="21">
         <v>29.40153096729297</v>
       </c>
-      <c r="P34" s="27">
+      <c r="P34" s="21">
         <v>28.398791540785499</v>
       </c>
-      <c r="Q34" s="27">
+      <c r="Q34" s="21">
         <v>30.2</v>
       </c>
-      <c r="R34" s="27">
+      <c r="R34" s="21">
         <v>22.8</v>
       </c>
-      <c r="S34" s="27">
+      <c r="S34" s="21">
         <v>20.801878879382652</v>
       </c>
-      <c r="T34" s="27">
+      <c r="T34" s="21">
         <v>47.832585949177876</v>
+      </c>
+      <c r="U34" s="21">
+        <v>34.917774273485016</v>
       </c>
     </row>
   </sheetData>
